--- a/Project_Plan.xlsx
+++ b/Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahul\Nyaymalaw 3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC5D109-54B7-4061-8E38-D96861ADB3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC8FA10-E99B-4B11-995C-90FACE86C23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
